--- a/04_Merchant_Banking/_template_LBO.xlsx
+++ b/04_Merchant_Banking/_template_LBO.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="77">
   <si>
     <t xml:space="preserve">[TARGET] — LBO Model</t>
   </si>
@@ -129,34 +129,58 @@
     <t xml:space="preserve">Yr5</t>
   </si>
   <si>
+    <t xml:space="preserve">Assumptions</t>
+  </si>
+  <si>
     <t xml:space="preserve">EBITDA</t>
   </si>
   <si>
+    <t xml:space="preserve">Entry EBITDA growth (%/yr)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cash flow available for debt paydown (FCF)</t>
   </si>
   <si>
+    <t xml:space="preserve">FCF conversion (FCF / EBITDA, %)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandatory amort (% of original TLB/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cash sweep (% of excess FCF, after debt svc)</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Beginning balance</t>
   </si>
   <si>
+    <t xml:space="preserve">Term Loan B interest rate (%)</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Mandatory amortization</t>
   </si>
   <si>
-    <t xml:space="preserve">  Cash sweep (excess FCF, 75%)</t>
+    <t xml:space="preserve">Original TLB balance (Yr0, $)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Cash sweep (excess FCF after debt svc)</t>
   </si>
   <si>
     <t xml:space="preserve">  Ending balance</t>
   </si>
   <si>
-    <t xml:space="preserve">  Interest expense (rate x avg balance)</t>
+    <t xml:space="preserve">Models Term Loan B only — the amortizing/sweep tranche in a typical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Interest expense (rate x beginning balance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">structure. Revolver stays undrawn at close; notes are bullet/no-amort.</t>
   </si>
   <si>
     <t xml:space="preserve">Total debt (end of period)</t>
   </si>
   <si>
     <t xml:space="preserve">Total debt / EBITDA (leverage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assumptions</t>
   </si>
   <si>
     <t xml:space="preserve">Returns — IRR / MOIC</t>
@@ -238,11 +262,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0;&quot;($&quot;#,##0\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0\x"/>
-    <numFmt numFmtId="167" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
+    <numFmt numFmtId="167" formatCode="0.00%;\(0.00%\);\-"/>
+    <numFmt numFmtId="168" formatCode="0.0\x"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -394,84 +419,112 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -728,62 +781,62 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="4"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="4" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>9</v>
       </c>
     </row>
@@ -804,128 +857,128 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F13"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="s">
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="C10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="8" t="n">
         <f aca="false">SUM(F5:F9)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <f aca="false">SUM(C5:C10)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="8" t="n">
+      <c r="C13" s="9" t="n">
         <f aca="false">C11-F10</f>
         <v>0</v>
       </c>
@@ -946,134 +999,355 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:H18"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="B2:K16"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="9" t="s">
+      <c r="E4" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="F4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="9" t="s">
+      <c r="H4" s="10" t="s">
         <v>33</v>
       </c>
+      <c r="J4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="10" t="s">
-        <v>34</v>
+      <c r="B5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <f aca="false">Returns!C5</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <f aca="false">C5*(1+$K$5)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <f aca="false">D5*(1+$K$5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <f aca="false">E5*(1+$K$5)</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="14" t="n">
+        <f aca="false">F5*(1+$K$5)</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="14" t="n">
+        <f aca="false">G5*(1+$K$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="10" t="s">
-        <v>35</v>
+      <c r="B6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="14" t="n">
+        <f aca="false">C5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="14" t="n">
+        <f aca="false">D5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <f aca="false">E5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <f aca="false">F5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <f aca="false">G5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <f aca="false">H5*$K$6</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J7" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="J8" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>0.75</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="11"/>
+      <c r="B9" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="16" t="n">
+        <f aca="false">$K$10</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="16" t="n">
+        <f aca="false">C12</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="16" t="n">
+        <f aca="false">D12</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <f aca="false">E12</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <f aca="false">F12</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <f aca="false">G12</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
+      <c r="B10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,C9)</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,D9)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,E9)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,F9)</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,G9)</f>
+        <v>0</v>
+      </c>
+      <c r="H10" s="16" t="n">
+        <f aca="false">MIN($K$10*$K$7,H9)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <f aca="false">'Sources &amp; Uses'!C7</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(C6-C10-C13)),C9-C10)</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(D6-D10-D13)),D9-D10)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(E6-E10-E13)),E9-E10)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(F6-F10-F13)),F9-F10)</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(G6-G10-G13)),G9-G10)</f>
+        <v>0</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <f aca="false">MIN(MAX(0,$K$8*(H6-H10-H13)),H9-H10)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="16" t="n">
+        <f aca="false">C9-C10-C11</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="16" t="n">
+        <f aca="false">D9-D10-D11</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <f aca="false">E9-E10-E11</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <f aca="false">F9-F10-F11</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <f aca="false">G9-G10-G11</f>
+        <v>0</v>
+      </c>
+      <c r="H12" s="16" t="n">
+        <f aca="false">H9-H10-H11</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
+      <c r="B13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13" s="16" t="n">
+        <f aca="false">C9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="16" t="n">
+        <f aca="false">D9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <f aca="false">E9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <f aca="false">F9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <f aca="false">G9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="16" t="n">
+        <f aca="false">H9*$K$9</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="19" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
+      <c r="B15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <f aca="false">C12</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <f aca="false">D12</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <f aca="false">E12</f>
+        <v>0</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">F12</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">G12</f>
+        <v>0</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <f aca="false">H12</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H18" s="2" t="s">
-        <v>43</v>
+      <c r="B16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="20" t="str">
+        <f aca="false">IFERROR(C15/C5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="D16" s="20" t="str">
+        <f aca="false">IFERROR(D15/D5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="E16" s="20" t="str">
+        <f aca="false">IFERROR(E15/E5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="F16" s="20" t="str">
+        <f aca="false">IFERROR(F15/F5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="G16" s="20" t="str">
+        <f aca="false">IFERROR(G15/G5,"-")</f>
+        <v>-</v>
+      </c>
+      <c r="H16" s="20" t="str">
+        <f aca="false">IFERROR(H15/H5,"-")</f>
+        <v>-</v>
       </c>
     </row>
   </sheetData>
@@ -1093,134 +1367,134 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:C20"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>44</v>
+      <c r="B2" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>45</v>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="13" t="n">
+      <c r="B5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="0" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="14" t="n">
+      <c r="B6" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="8" t="n">
+      <c r="B7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <f aca="false">C5*C6</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="15" t="n">
+      <c r="B8" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="23" t="n">
         <f aca="false">'Sources &amp; Uses'!C9</f>
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="4" t="s">
-        <v>50</v>
+      <c r="B10" s="5" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="C11" s="15" t="n">
+      <c r="B11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="23" t="n">
         <f aca="false">'Debt Schedule'!H5</f>
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="14" t="n">
+      <c r="B12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="8" t="n">
+      <c r="B13" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="9" t="n">
         <f aca="false">C11*C12</f>
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="15" t="n">
+      <c r="B14" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14" s="23" t="n">
         <f aca="false">'Debt Schedule'!H15</f>
         <v>0</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="0" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="7" t="n">
+      <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="8" t="n">
         <f aca="false">C13-C14</f>
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="4" t="s">
-        <v>56</v>
+      <c r="B17" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="0" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="16" t="str">
+      <c r="B18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="24" t="str">
         <f aca="false">IFERROR(C15/C8,"-")</f>
         <v>-</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="10" t="n">
+      <c r="B19" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="12" t="n">
         <f aca="false">Cover!C8</f>
         <v>5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="17" t="str">
+      <c r="B20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="25" t="str">
         <f aca="false">IFERROR(C18^(1/C19)-1,"-")</f>
         <v>-</v>
       </c>
@@ -1242,136 +1516,136 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="12"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>60</v>
+      <c r="B2" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="18" t="n">
+      <c r="B4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C4" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="18" t="n">
+      <c r="D4" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="18" t="n">
+      <c r="F4" s="26" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="18" t="n">
+      <c r="G4" s="26" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="18" t="n">
+      <c r="B5" s="26" t="n">
         <v>6</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="18" t="n">
+      <c r="B6" s="26" t="n">
         <v>7</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="18" t="n">
+      <c r="B7" s="26" t="n">
         <v>8</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G7" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="18" t="n">
+      <c r="B8" s="26" t="n">
         <v>9</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="18" t="n">
+      <c r="B9" s="26" t="n">
         <v>10</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1391,35 +1665,35 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="B2:F4"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>63</v>
+      <c r="B2" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>68</v>
+      <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>

--- a/04_Merchant_Banking/_template_LBO.xlsx
+++ b/04_Merchant_Banking/_template_LBO.xlsx
@@ -1,120 +1,91 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sources &amp; Uses" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Operating Model" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Debt Schedule" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Covenants" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Management Equity" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Returns Waterfall" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Checks" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="Sources" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Institutional Surface" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Challenge Log" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lineage Map" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources &amp; Uses" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operating Model" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenants" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Management Equity" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Returns Waterfall" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RefreshLog" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="FS_MODEL_ID">'Institutional Surface'!$C$4</definedName>
     <definedName name="FS_DOMAIN">'Institutional Surface'!$C$5</definedName>
     <definedName name="FS_MATURITY">'Institutional Surface'!$C$6</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001" forceFullCalc="1"/>
+  <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="\$#,##0.0;[RED]&quot;($&quot;#,##0.0\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.0%;[RED]\(0.0%\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.00%;[RED]\(0.00%\);\-"/>
-    <numFmt numFmtId="167" formatCode="0.0\x;[RED]\(0.0&quot;x)&quot;;\-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.0;[Red]($#,##0.0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);-"/>
+    <numFmt numFmtId="166" formatCode="0.00%;[Red](0.00%);-"/>
+    <numFmt numFmtId="167" formatCode="0.0x;[Red](0.0x);-"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
-      <charset val="1"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="0"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="16"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF111827"/>
+      <color rgb="00111827"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF0000FF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <color rgb="FF111827"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="0"/>
-      <b val="1"/>
-      <color rgb="FF008000"/>
+      <color rgb="00008000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -139,14 +110,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
-        <bgColor rgb="FF003366"/>
+        <fgColor rgb="001F4E78"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFCE4D6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -169,22 +138,14 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
       <top style="thin">
-        <color rgb="FF111827"/>
+        <color rgb="00111827"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
     <border>
       <bottom style="thin">
@@ -192,305 +153,184 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <dxfs count="3">
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFE2F0D9"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00E2F0D9"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFCE4D6"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FCE4D6"/>
         </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF2CC"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFBFBFBF"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFF2CC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFE2F0D9"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFCE4D6"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF111827"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF1F4E78"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -498,294 +338,404 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F17"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="36" customWidth="1" style="25" min="2" max="2"/>
-    <col width="46" customWidth="1" style="25" min="3" max="3"/>
-    <col width="12" customWidth="1" style="25" min="4" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>[TARGET] — LBO Underwriting Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="28" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Target / transaction:</t>
         </is>
       </c>
-      <c r="C4" s="29" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>[Name]</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="28" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Sponsor / principal:</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>[Fund / merchant bank]</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="28" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Entry / close date:</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="28" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>Last refreshed:</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="28" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>Next IC / financing event:</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="28" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>Active scenario:</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="28" t="inlineStr">
+    <row r="10">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Units:</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>$ in millions unless noted</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="30" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Modeling conventions</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="31" t="inlineStr">
+    <row r="14">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Blue text / yellow fill</t>
         </is>
       </c>
-      <c r="C14" s="32" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>Hardcoded input or selected scenario</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="28" t="inlineStr">
+    <row r="15">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C15" s="32" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>Formula / same-sheet calculation</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="B16" s="33" t="inlineStr">
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Green text</t>
         </is>
       </c>
-      <c r="C16" s="32" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>Cross-sheet formula / link</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="B17" s="28" t="inlineStr">
+    <row r="17">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Checks</t>
         </is>
       </c>
-      <c r="C17" s="32" t="inlineStr">
+      <c r="C17" s="6" t="inlineStr">
         <is>
           <t>PASS / REVIEW / FAIL must remain visible</t>
         </is>
@@ -797,162 +747,159 @@
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"Base,Downside"</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="34" customWidth="1" style="25" min="2" max="2"/>
-    <col width="18" customWidth="1" style="25" min="3" max="3"/>
-    <col width="16" customWidth="1" style="25" min="4" max="4"/>
-    <col width="42" customWidth="1" style="25" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Management Equity and Incentive Pool</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Management fully diluted pool</t>
         </is>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="12">
         <f>Assumptions!E30</f>
         <v/>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>granted / reserved pool</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Sponsor ownership before pool</t>
         </is>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="12">
         <f>1-C5</f>
         <v/>
       </c>
-      <c r="D6" s="25" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>fully diluted</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Sponsor invested equity</t>
         </is>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="10">
         <f>'Sources &amp; Uses'!F8</f>
         <v/>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>entry equity</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Preferred return at exit</t>
         </is>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="10">
         <f>C7*(1+Assumptions!E31)^Assumptions!E29</f>
         <v/>
       </c>
-      <c r="D8" s="25" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sponsor hurdle</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Management catch-up rate</t>
         </is>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="12">
         <f>Assumptions!E32</f>
         <v/>
       </c>
-      <c r="D9" s="25" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>% incremental</t>
         </is>
       </c>
-      <c r="E9" s="25" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>above preferred return</t>
         </is>
@@ -962,505 +909,510 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:J15"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="34" customWidth="1" style="25" min="2" max="2"/>
-    <col width="13" customWidth="1" style="25" min="3" max="10"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Exit Equity and Sponsor / Management Waterfall</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Selected exit</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Exit EBITDA</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="10">
         <f>'Operating Model'!D8</f>
         <v/>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="10">
         <f>'Operating Model'!E8</f>
         <v/>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="10">
         <f>'Operating Model'!F8</f>
         <v/>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="10">
         <f>'Operating Model'!G8</f>
         <v/>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="10">
         <f>'Operating Model'!H8</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="10">
         <f>'Operating Model'!I8</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="10">
         <f>'Operating Model'!J8</f>
         <v/>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="10">
         <f>INDEX(C5:I5,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Exit multiple</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="16">
         <f>Assumptions!$E$28</f>
         <v/>
       </c>
-      <c r="J6" s="47">
+      <c r="J6" s="16">
         <f>INDEX(C6:I6,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Exit enterprise value</t>
         </is>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="10">
         <f>C5*C6</f>
         <v/>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="10">
         <f>D5*D6</f>
         <v/>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="10">
         <f>E5*E6</f>
         <v/>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="10">
         <f>F5*F6</f>
         <v/>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="10">
         <f>G5*G6</f>
         <v/>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="10">
         <f>H5*H6</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="10">
         <f>I5*I6</f>
         <v/>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="10">
         <f>INDEX(C7:I7,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Net debt</t>
         </is>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="10">
         <f>'Debt Schedule'!D28</f>
         <v/>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="10">
         <f>'Debt Schedule'!E28</f>
         <v/>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="10">
         <f>'Debt Schedule'!F28</f>
         <v/>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="10">
         <f>'Debt Schedule'!G28</f>
         <v/>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="10">
         <f>'Debt Schedule'!H28</f>
         <v/>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="10">
         <f>'Debt Schedule'!I28</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="10">
         <f>'Debt Schedule'!J28</f>
         <v/>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="10">
         <f>INDEX(C8:I8,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Gross equity value</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="10">
         <f>MAX(0,C7-C8)</f>
         <v/>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="10">
         <f>MAX(0,D7-D8)</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="10">
         <f>MAX(0,E7-E8)</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="10">
         <f>MAX(0,F7-F8)</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="10">
         <f>MAX(0,G7-G8)</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="10">
         <f>MAX(0,H7-H8)</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="10">
         <f>MAX(0,I7-I8)</f>
         <v/>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="10">
         <f>INDEX(C9:I9,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Sponsor preferred return</t>
         </is>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^1</f>
         <v/>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^2</f>
         <v/>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^3</f>
         <v/>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^4</f>
         <v/>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^5</f>
         <v/>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^6</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="10">
         <f>'Management Equity'!$C$7*(1+Assumptions!$E$31)^7</f>
         <v/>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="10">
         <f>INDEX(C10:I10,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Equity above preferred</t>
         </is>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="10">
         <f>MAX(0,C9-C10)</f>
         <v/>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="10">
         <f>MAX(0,D9-D10)</f>
         <v/>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="10">
         <f>MAX(0,E9-E10)</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="10">
         <f>MAX(0,F9-F10)</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="10">
         <f>MAX(0,G9-G10)</f>
         <v/>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="10">
         <f>MAX(0,H9-H10)</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="10">
         <f>MAX(0,I9-I10)</f>
         <v/>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="10">
         <f>INDEX(C11:I11,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Management proceeds</t>
         </is>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="10">
         <f>MIN(C9,C9*Assumptions!$E$30+C11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="10">
         <f>MIN(D9,D9*Assumptions!$E$30+D11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="10">
         <f>MIN(E9,E9*Assumptions!$E$30+E11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="10">
         <f>MIN(F9,F9*Assumptions!$E$30+F11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="10">
         <f>MIN(G9,G9*Assumptions!$E$30+G11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="10">
         <f>MIN(H9,H9*Assumptions!$E$30+H11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="10">
         <f>MIN(I9,I9*Assumptions!$E$30+I11*Assumptions!$E$32)</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="10">
         <f>INDEX(C12:I12,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="25" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Sponsor proceeds</t>
         </is>
       </c>
-      <c r="C13" s="41">
+      <c r="C13" s="10">
         <f>MAX(0,C9-C12)</f>
         <v/>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="10">
         <f>MAX(0,D9-D12)</f>
         <v/>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="10">
         <f>MAX(0,E9-E12)</f>
         <v/>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="10">
         <f>MAX(0,F9-F12)</f>
         <v/>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="10">
         <f>MAX(0,G9-G12)</f>
         <v/>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="10">
         <f>MAX(0,H9-H12)</f>
         <v/>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="10">
         <f>MAX(0,I9-I12)</f>
         <v/>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="10">
         <f>INDEX(C13:I13,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="25" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Sponsor MOIC</t>
         </is>
       </c>
-      <c r="C14" s="47">
+      <c r="C14" s="16">
         <f>IFERROR(C13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="D14" s="47">
+      <c r="D14" s="16">
         <f>IFERROR(D13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="E14" s="47">
+      <c r="E14" s="16">
         <f>IFERROR(E13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="F14" s="47">
+      <c r="F14" s="16">
         <f>IFERROR(F13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="16">
         <f>IFERROR(G13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="H14" s="47">
+      <c r="H14" s="16">
         <f>IFERROR(H13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="I14" s="47">
+      <c r="I14" s="16">
         <f>IFERROR(I13/'Sources &amp; Uses'!$F$8,0)</f>
         <v/>
       </c>
-      <c r="J14" s="47">
+      <c r="J14" s="16">
         <f>INDEX(C14:I14,1,Assumptions!E29)</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="25" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Sponsor IRR</t>
         </is>
       </c>
-      <c r="C15" s="45">
+      <c r="C15" s="14">
         <f>IFERROR((C13/'Sources &amp; Uses'!$F$8)^(1/1)-1,0)</f>
         <v/>
       </c>
-      <c r="D15" s="45">
+      <c r="D15" s="14">
         <f>IFERROR((D13/'Sources &amp; Uses'!$F$8)^(1/2)-1,0)</f>
         <v/>
       </c>
-      <c r="E15" s="45">
+      <c r="E15" s="14">
         <f>IFERROR((E13/'Sources &amp; Uses'!$F$8)^(1/3)-1,0)</f>
         <v/>
       </c>
-      <c r="F15" s="45">
+      <c r="F15" s="14">
         <f>IFERROR((F13/'Sources &amp; Uses'!$F$8)^(1/4)-1,0)</f>
         <v/>
       </c>
-      <c r="G15" s="45">
+      <c r="G15" s="14">
         <f>IFERROR((G13/'Sources &amp; Uses'!$F$8)^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="H15" s="45">
+      <c r="H15" s="14">
         <f>IFERROR((H13/'Sources &amp; Uses'!$F$8)^(1/6)-1,0)</f>
         <v/>
       </c>
-      <c r="I15" s="45">
+      <c r="I15" s="14">
         <f>IFERROR((I13/'Sources &amp; Uses'!$F$8)^(1/7)-1,0)</f>
         <v/>
       </c>
-      <c r="J15" s="45">
+      <c r="J15" s="14">
         <f>INDEX(C15:I15,1,Assumptions!E29)</f>
         <v/>
       </c>
@@ -1469,176 +1421,178 @@
   <mergeCells count="1">
     <mergeCell ref="B2:J2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="28" customWidth="1" style="25" min="2" max="2"/>
-    <col width="14" customWidth="1" style="25" min="3" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Sponsor IRR Sensitivity</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Entry / Exit multiple</t>
         </is>
       </c>
-      <c r="C4" s="52" t="n">
+      <c r="C4" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="D4" s="52" t="n">
+      <c r="D4" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="E4" s="52" t="n">
+      <c r="E4" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="F4" s="52" t="n">
+      <c r="F4" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="G4" s="52" t="n">
+      <c r="G4" s="21" t="n">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="47" t="n">
+    <row r="5">
+      <c r="B5" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="12">
         <f>IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="12">
         <f>IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="12">
         <f>IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="12">
         <f>IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="G5" s="43">
+      <c r="G5" s="12">
         <f>IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B5+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="47" t="n">
+    <row r="6">
+      <c r="B6" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="C6" s="43">
+      <c r="C6" s="12">
         <f>IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="12">
         <f>IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="12">
         <f>IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="12">
         <f>IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="12">
         <f>IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B6+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="47" t="n">
+    <row r="7">
+      <c r="B7" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="12">
         <f>IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="D7" s="43">
+      <c r="D7" s="12">
         <f>IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="12">
         <f>IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="12">
         <f>IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="G7" s="43">
+      <c r="G7" s="12">
         <f>IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B7+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="47" t="n">
+    <row r="8">
+      <c r="B8" s="16" t="n">
         <v>11</v>
       </c>
-      <c r="C8" s="43">
+      <c r="C8" s="12">
         <f>IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="D8" s="43">
+      <c r="D8" s="12">
         <f>IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="E8" s="43">
+      <c r="E8" s="12">
         <f>IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="12">
         <f>IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="G8" s="43">
+      <c r="G8" s="12">
         <f>IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B8+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="47" t="n">
+    <row r="9">
+      <c r="B9" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C9" s="43">
+      <c r="C9" s="12">
         <f>IFERROR(((('Operating Model'!H8*C$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="D9" s="43">
+      <c r="D9" s="12">
         <f>IFERROR(((('Operating Model'!H8*D$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="12">
         <f>IFERROR(((('Operating Model'!H8*E$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="12">
         <f>IFERROR(((('Operating Model'!H8*F$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
-      <c r="G9" s="43">
+      <c r="G9" s="12">
         <f>IFERROR(((('Operating Model'!H8*G$4-'Debt Schedule'!G28)*(1-Assumptions!$E$30))/MAX(0.01,('Operating Model'!C8*$B9+Assumptions!$E$15+'Sources &amp; Uses'!C7+Assumptions!$E$16-'Sources &amp; Uses'!F6-'Sources &amp; Uses'!F7)))^(1/5)-1,0)</f>
         <v/>
       </c>
@@ -1648,151 +1602,149 @@
     <mergeCell ref="B2:G2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:G9">
-    <cfRule type="colorScale" priority="2">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min" val="0"/>
+        <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
+        <cfvo type="max"/>
+        <color rgb="00FCE4D6"/>
+        <color rgb="00FFF2CC"/>
+        <color rgb="00E2F0D9"/>
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:C13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="46" customWidth="1" style="25" min="2" max="2"/>
-    <col width="18" customWidth="1" style="25" min="3" max="3"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>LBO Model Checks</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Check</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Sources equal uses</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5">
         <f>IF(ABS('Sources &amp; Uses'!F10)&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Sponsor equity positive</t>
         </is>
       </c>
-      <c r="C6" s="25">
+      <c r="C6">
         <f>IF('Sources &amp; Uses'!F8&gt;0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Debt balances nonnegative</t>
         </is>
       </c>
-      <c r="C7" s="25">
+      <c r="C7">
         <f>IF(MIN('Debt Schedule'!D15:J25)&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Cash at or above minimum</t>
         </is>
       </c>
-      <c r="C8" s="25">
+      <c r="C8">
         <f>IF(MIN('Debt Schedule'!D13:J13)&gt;=Assumptions!E16,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>No covenant breaches</t>
         </is>
       </c>
-      <c r="C9" s="25">
+      <c r="C9">
         <f>IF(COUNTIF(Covenants!C13:I13,"BREACH")=0,"PASS","REVIEW")</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Exit equity nonnegative</t>
         </is>
       </c>
-      <c r="C10" s="25">
+      <c r="C10">
         <f>IF(MIN('Returns Waterfall'!C9:I9)&gt;=0,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Waterfall conserves equity</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11">
         <f>IF(MAX(ABS('Returns Waterfall'!C9:I9-'Returns Waterfall'!C12:I12-'Returns Waterfall'!C13:I13))&lt;0.000001,"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Selected exit year valid</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12">
         <f>IF(AND(Assumptions!E29&gt;=1,Assumptions!E29&lt;=7),"PASS","FAIL")</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="25" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13">
         <f>IF(COUNTIF(C5:C12,"FAIL")=0,"PASS","FAIL")</f>
         <v/>
       </c>
@@ -1802,175 +1754,173 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <conditionalFormatting sqref="C5:C13">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C5="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C5="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C5="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C5="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:E9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="34" customWidth="1" style="25" min="2" max="2"/>
-    <col width="58" customWidth="1" style="25" min="3" max="3"/>
-    <col width="16" customWidth="1" style="25" min="4" max="4"/>
-    <col width="48" customWidth="1" style="25" min="5" max="5"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Source Register</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Input / dataset</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Source URL or document</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Notes / transformation</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="53" t="inlineStr">
+    <row r="5">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Historical financial statements</t>
         </is>
       </c>
-      <c r="C5" s="53" t="inlineStr">
+      <c r="C5" s="22" t="inlineStr">
         <is>
           <t>[filing / data room URL]</t>
         </is>
       </c>
-      <c r="D5" s="53" t="inlineStr">
+      <c r="D5" s="22" t="inlineStr">
         <is>
           <t>[period]</t>
         </is>
       </c>
-      <c r="E5" s="53" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>Revenue, margins, capex, working capital, taxes</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="53" t="inlineStr">
+    <row r="6">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>Quality of earnings and diligence</t>
         </is>
       </c>
-      <c r="C6" s="53" t="inlineStr">
+      <c r="C6" s="22" t="inlineStr">
         <is>
           <t>[advisor report URL]</t>
         </is>
       </c>
-      <c r="D6" s="53" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E6" s="53" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t>EBITDA adjustments, one-time items, risks</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="53" t="inlineStr">
+    <row r="7">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>Debt term sheets and documentation</t>
         </is>
       </c>
-      <c r="C7" s="53" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t>[data room URL]</t>
         </is>
       </c>
-      <c r="D7" s="53" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E7" s="53" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t>Rates, PIK, amortization, sweeps, covenants, baskets</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="53" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>Transaction terms</t>
         </is>
       </c>
-      <c r="C8" s="53" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>[purchase agreement / process letter]</t>
         </is>
       </c>
-      <c r="D8" s="53" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E8" s="53" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>Price, fees, minimum cash, rollover, management pool</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="53" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>Market valuation references</t>
         </is>
       </c>
-      <c r="C9" s="53" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>[public market / transaction source]</t>
         </is>
       </c>
-      <c r="D9" s="53" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>[date]</t>
         </is>
       </c>
-      <c r="E9" s="53" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>Entry and exit multiple support</t>
         </is>
@@ -1980,276 +1930,272 @@
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="14" customWidth="1" style="25" min="2" max="2"/>
-    <col width="22" customWidth="1" style="25" min="3" max="3"/>
-    <col width="28" customWidth="1" style="25" min="4" max="4"/>
-    <col width="38" customWidth="1" style="25" min="5" max="5"/>
-    <col width="34" customWidth="1" style="25" min="6" max="6"/>
-    <col width="18" customWidth="1" style="25" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Refresh Log</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Trigger</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Source snapshot</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>What changed</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Reviewer / challenge</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Next check</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="54" t="n"/>
-      <c r="C5" s="54" t="n"/>
-      <c r="D5" s="54" t="n"/>
-      <c r="E5" s="54" t="n"/>
-      <c r="F5" s="54" t="n"/>
-      <c r="G5" s="54" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="54" t="n"/>
-      <c r="C6" s="54" t="n"/>
-      <c r="D6" s="54" t="n"/>
-      <c r="E6" s="54" t="n"/>
-      <c r="F6" s="54" t="n"/>
-      <c r="G6" s="54" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="54" t="n"/>
-      <c r="C7" s="54" t="n"/>
-      <c r="D7" s="54" t="n"/>
-      <c r="E7" s="54" t="n"/>
-      <c r="F7" s="54" t="n"/>
-      <c r="G7" s="54" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="54" t="n"/>
-      <c r="C8" s="54" t="n"/>
-      <c r="D8" s="54" t="n"/>
-      <c r="E8" s="54" t="n"/>
-      <c r="F8" s="54" t="n"/>
-      <c r="G8" s="54" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="54" t="n"/>
-      <c r="C9" s="54" t="n"/>
-      <c r="D9" s="54" t="n"/>
-      <c r="E9" s="54" t="n"/>
-      <c r="F9" s="54" t="n"/>
-      <c r="G9" s="54" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="54" t="n"/>
-      <c r="C10" s="54" t="n"/>
-      <c r="D10" s="54" t="n"/>
-      <c r="E10" s="54" t="n"/>
-      <c r="F10" s="54" t="n"/>
-      <c r="G10" s="54" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="54" t="n"/>
-      <c r="C11" s="54" t="n"/>
-      <c r="D11" s="54" t="n"/>
-      <c r="E11" s="54" t="n"/>
-      <c r="F11" s="54" t="n"/>
-      <c r="G11" s="54" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="54" t="n"/>
-      <c r="C12" s="54" t="n"/>
-      <c r="D12" s="54" t="n"/>
-      <c r="E12" s="54" t="n"/>
-      <c r="F12" s="54" t="n"/>
-      <c r="G12" s="54" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="54" t="n"/>
-      <c r="C13" s="54" t="n"/>
-      <c r="D13" s="54" t="n"/>
-      <c r="E13" s="54" t="n"/>
-      <c r="F13" s="54" t="n"/>
-      <c r="G13" s="54" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="54" t="n"/>
-      <c r="C14" s="54" t="n"/>
-      <c r="D14" s="54" t="n"/>
-      <c r="E14" s="54" t="n"/>
-      <c r="F14" s="54" t="n"/>
-      <c r="G14" s="54" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="54" t="n"/>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="54" t="n"/>
-      <c r="E15" s="54" t="n"/>
-      <c r="F15" s="54" t="n"/>
-      <c r="G15" s="54" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="B16" s="54" t="n"/>
-      <c r="C16" s="54" t="n"/>
-      <c r="D16" s="54" t="n"/>
-      <c r="E16" s="54" t="n"/>
-      <c r="F16" s="54" t="n"/>
-      <c r="G16" s="54" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="B17" s="54" t="n"/>
-      <c r="C17" s="54" t="n"/>
-      <c r="D17" s="54" t="n"/>
-      <c r="E17" s="54" t="n"/>
-      <c r="F17" s="54" t="n"/>
-      <c r="G17" s="54" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="26">
-      <c r="B18" s="54" t="n"/>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="54" t="n"/>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="54" t="n"/>
-      <c r="G18" s="54" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="26">
-      <c r="B19" s="54" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="54" t="n"/>
-      <c r="G19" s="54" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="26">
-      <c r="B20" s="54" t="n"/>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="54" t="n"/>
-      <c r="G20" s="54" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="26">
-      <c r="B21" s="54" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="54" t="n"/>
-      <c r="G21" s="54" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="26">
-      <c r="B22" s="54" t="n"/>
-      <c r="C22" s="54" t="n"/>
-      <c r="D22" s="54" t="n"/>
-      <c r="E22" s="54" t="n"/>
-      <c r="F22" s="54" t="n"/>
-      <c r="G22" s="54" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="26">
-      <c r="B23" s="54" t="n"/>
-      <c r="C23" s="54" t="n"/>
-      <c r="D23" s="54" t="n"/>
-      <c r="E23" s="54" t="n"/>
-      <c r="F23" s="54" t="n"/>
-      <c r="G23" s="54" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="26">
-      <c r="B24" s="54" t="n"/>
-      <c r="C24" s="54" t="n"/>
-      <c r="D24" s="54" t="n"/>
-      <c r="E24" s="54" t="n"/>
-      <c r="F24" s="54" t="n"/>
-      <c r="G24" s="54" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="26">
-      <c r="B25" s="54" t="n"/>
-      <c r="C25" s="54" t="n"/>
-      <c r="D25" s="54" t="n"/>
-      <c r="E25" s="54" t="n"/>
-      <c r="F25" s="54" t="n"/>
-      <c r="G25" s="54" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="26">
-      <c r="B26" s="54" t="n"/>
-      <c r="C26" s="54" t="n"/>
-      <c r="D26" s="54" t="n"/>
-      <c r="E26" s="54" t="n"/>
-      <c r="F26" s="54" t="n"/>
-      <c r="G26" s="54" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="26">
-      <c r="B27" s="54" t="n"/>
-      <c r="C27" s="54" t="n"/>
-      <c r="D27" s="54" t="n"/>
-      <c r="E27" s="54" t="n"/>
-      <c r="F27" s="54" t="n"/>
-      <c r="G27" s="54" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="26">
-      <c r="B28" s="54" t="n"/>
-      <c r="C28" s="54" t="n"/>
-      <c r="D28" s="54" t="n"/>
-      <c r="E28" s="54" t="n"/>
-      <c r="F28" s="54" t="n"/>
-      <c r="G28" s="54" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="26">
-      <c r="B29" s="54" t="n"/>
-      <c r="C29" s="54" t="n"/>
-      <c r="D29" s="54" t="n"/>
-      <c r="E29" s="54" t="n"/>
-      <c r="F29" s="54" t="n"/>
-      <c r="G29" s="54" t="n"/>
+    <row r="5">
+      <c r="B5" s="23" t="n"/>
+      <c r="C5" s="23" t="n"/>
+      <c r="D5" s="23" t="n"/>
+      <c r="E5" s="23" t="n"/>
+      <c r="F5" s="23" t="n"/>
+      <c r="G5" s="23" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="23" t="n"/>
+      <c r="C6" s="23" t="n"/>
+      <c r="D6" s="23" t="n"/>
+      <c r="E6" s="23" t="n"/>
+      <c r="F6" s="23" t="n"/>
+      <c r="G6" s="23" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="23" t="n"/>
+      <c r="C7" s="23" t="n"/>
+      <c r="D7" s="23" t="n"/>
+      <c r="E7" s="23" t="n"/>
+      <c r="F7" s="23" t="n"/>
+      <c r="G7" s="23" t="n"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="23" t="n"/>
+      <c r="D8" s="23" t="n"/>
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+    </row>
+    <row r="9">
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="23" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="23" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="23" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="23" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="23" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="23" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="23" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="23" t="n"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="23" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="23" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="23" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="23" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="23" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="23" t="n"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="23" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="23" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="23" t="n"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="23" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="23" t="n"/>
+      <c r="F22" s="23" t="n"/>
+      <c r="G22" s="23" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="23" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="23" t="n"/>
+      <c r="F23" s="23" t="n"/>
+      <c r="G23" s="23" t="n"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="23" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="23" t="n"/>
+      <c r="F24" s="23" t="n"/>
+      <c r="G24" s="23" t="n"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="23" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="23" t="n"/>
+      <c r="F25" s="23" t="n"/>
+      <c r="G25" s="23" t="n"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="23" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="23" t="n"/>
+      <c r="F26" s="23" t="n"/>
+      <c r="G26" s="23" t="n"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="23" t="n"/>
+      <c r="F27" s="23" t="n"/>
+      <c r="G27" s="23" t="n"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="23" t="n"/>
+      <c r="F28" s="23" t="n"/>
+      <c r="G28" s="23" t="n"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="23" t="n"/>
+      <c r="F29" s="23" t="n"/>
+      <c r="G29" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2262,133 +2208,133 @@
   <dimension ref="B2:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" style="26" min="2" max="2"/>
-    <col width="48" customWidth="1" style="26" min="3" max="3"/>
-    <col width="24" customWidth="1" style="26" min="4" max="4"/>
-    <col width="34" customWidth="1" style="26" min="5" max="5"/>
-    <col width="20" customWidth="1" style="26" min="6" max="6"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>Merchant Banking — Institutional Decision Surface</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="35" t="inlineStr">
+      <c r="B4" s="25" t="inlineStr">
         <is>
           <t>Model ID</t>
         </is>
       </c>
-      <c r="C4" s="36" t="inlineStr">
+      <c r="C4" s="26" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="25" t="inlineStr">
         <is>
           <t>Domain</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="26" t="inlineStr">
         <is>
           <t>Merchant Banking</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="25" t="inlineStr">
         <is>
           <t>Declared maturity</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="25" t="inlineStr">
         <is>
           <t>Canonical builder</t>
         </is>
       </c>
-      <c r="C7" s="36" t="inlineStr">
+      <c r="C7" s="26" t="inlineStr">
         <is>
           <t>tools/builders/build_lbo_release.py</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>Decision arena</t>
         </is>
       </c>
-      <c r="C8" s="36" t="inlineStr">
+      <c r="C8" s="26" t="inlineStr">
         <is>
           <t>principal investing committee, client coverage, financing partners and risk committee</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>Committee artifact</t>
         </is>
       </c>
-      <c r="C9" s="36" t="inlineStr">
+      <c r="C9" s="26" t="inlineStr">
         <is>
           <t>principal-and-advisory conflicts pack</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
         <is>
           <t>Operating cadence</t>
         </is>
       </c>
-      <c r="C10" s="36" t="inlineStr">
+      <c r="C10" s="26" t="inlineStr">
         <is>
           <t>daily live transactions; weekly risk; monthly portfolio</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="37" t="inlineStr">
+      <c r="B12" s="27" t="inlineStr">
         <is>
           <t>Key decision outputs</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C13" s="38" t="inlineStr">
+      <c r="C13" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D13" s="38" t="inlineStr">
+      <c r="D13" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E13" s="38" t="inlineStr">
+      <c r="E13" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F13" s="38" t="inlineStr">
+      <c r="F13" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2480,34 +2426,34 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="37" t="inlineStr">
+      <c r="B20" s="27" t="inlineStr">
         <is>
           <t>Insider questions</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="38" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C21" s="38" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D21" s="38" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E21" s="38" t="inlineStr">
+      <c r="E21" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F21" s="38" t="inlineStr">
+      <c r="F21" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2599,34 +2545,34 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="37" t="inlineStr">
+      <c r="B28" s="27" t="inlineStr">
         <is>
           <t>Scenario families</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="38" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D29" s="38" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="E29" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F29" s="38" t="inlineStr">
+      <c r="F29" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2718,34 +2664,34 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="37" t="inlineStr">
+      <c r="B36" s="27" t="inlineStr">
         <is>
           <t>Primary diligence documents</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="38" t="inlineStr">
+      <c r="B37" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C37" s="38" t="inlineStr">
+      <c r="C37" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D37" s="38" t="inlineStr">
+      <c r="D37" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E37" s="38" t="inlineStr">
+      <c r="E37" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F37" s="38" t="inlineStr">
+      <c r="F37" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2837,34 +2783,34 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="37" t="inlineStr">
+      <c r="B44" s="27" t="inlineStr">
         <is>
           <t>Challenge tests</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="38" t="inlineStr">
+      <c r="B45" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C45" s="38" t="inlineStr">
+      <c r="C45" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D45" s="38" t="inlineStr">
+      <c r="D45" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E45" s="38" t="inlineStr">
+      <c r="E45" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F45" s="38" t="inlineStr">
+      <c r="F45" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -2956,34 +2902,34 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="37" t="inlineStr">
+      <c r="B52" s="27" t="inlineStr">
         <is>
           <t>Known failure modes</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="38" t="inlineStr">
+      <c r="B53" s="28" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="28" t="inlineStr">
         <is>
           <t>Requirement</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
+      <c r="D53" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="E53" s="38" t="inlineStr">
+      <c r="E53" s="28" t="inlineStr">
         <is>
           <t>Evidence / location</t>
         </is>
       </c>
-      <c r="F53" s="38" t="inlineStr">
+      <c r="F53" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3075,34 +3021,34 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="37" t="inlineStr">
+      <c r="B60" s="27" t="inlineStr">
         <is>
           <t>Regulatory / methodological anchors</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="38" t="inlineStr">
+      <c r="B61" s="28" t="inlineStr">
         <is>
           <t>Standard</t>
         </is>
       </c>
-      <c r="C61" s="38" t="inlineStr">
+      <c r="C61" s="28" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="D61" s="38" t="inlineStr">
+      <c r="D61" s="28" t="inlineStr">
         <is>
           <t>Source URL</t>
         </is>
       </c>
-      <c r="E61" s="38" t="inlineStr">
+      <c r="E61" s="28" t="inlineStr">
         <is>
           <t>Applicability</t>
         </is>
       </c>
-      <c r="F61" s="38" t="inlineStr">
+      <c r="F61" s="28" t="inlineStr">
         <is>
           <t>Review note</t>
         </is>
@@ -3205,60 +3151,60 @@
   <dimension ref="B2:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" style="26" min="2" max="2"/>
-    <col width="22" customWidth="1" style="26" min="3" max="3"/>
-    <col width="52" customWidth="1" style="26" min="4" max="4"/>
-    <col width="46" customWidth="1" style="26" min="5" max="5"/>
-    <col width="36" customWidth="1" style="26" min="6" max="6"/>
-    <col width="14" customWidth="1" style="26" min="7" max="7"/>
-    <col width="18" customWidth="1" style="26" min="8" max="8"/>
-    <col width="14" customWidth="1" style="26" min="9" max="9"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>Independent Challenge, Override and Closure Log</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Reviewer</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Challenge</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>Owner response</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="G4" s="38" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="H4" s="38" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I4" s="38" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>Closure</t>
         </is>
@@ -3379,66 +3325,66 @@
   <dimension ref="B2:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="26" min="2" max="2"/>
-    <col width="18" customWidth="1" style="26" min="3" max="3"/>
-    <col width="42" customWidth="1" style="26" min="4" max="4"/>
-    <col width="24" customWidth="1" style="26" min="5" max="5"/>
-    <col width="18" customWidth="1" style="26" min="6" max="6"/>
-    <col width="22" customWidth="1" style="26" min="7" max="7"/>
-    <col width="42" customWidth="1" style="26" min="8" max="8"/>
-    <col width="30" customWidth="1" style="26" min="9" max="9"/>
-    <col width="15" customWidth="1" style="26" min="10" max="10"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="2">
-      <c r="B2" s="34" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>Source, Transformation, Ownership and Refresh Map</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="28" t="inlineStr">
         <is>
           <t>Source class</t>
         </is>
       </c>
-      <c r="C4" s="38" t="inlineStr">
+      <c r="C4" s="28" t="inlineStr">
         <is>
           <t>Cadence</t>
         </is>
       </c>
-      <c r="D4" s="38" t="inlineStr">
+      <c r="D4" s="28" t="inlineStr">
         <is>
           <t>Control</t>
         </is>
       </c>
-      <c r="E4" s="38" t="inlineStr">
+      <c r="E4" s="28" t="inlineStr">
         <is>
           <t>System / provider</t>
         </is>
       </c>
-      <c r="F4" s="38" t="inlineStr">
+      <c r="F4" s="28" t="inlineStr">
         <is>
           <t>As-of</t>
         </is>
       </c>
-      <c r="G4" s="38" t="inlineStr">
+      <c r="G4" s="28" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="38" t="inlineStr">
+      <c r="H4" s="28" t="inlineStr">
         <is>
           <t>Transform</t>
         </is>
       </c>
-      <c r="I4" s="38" t="inlineStr">
+      <c r="I4" s="28" t="inlineStr">
         <is>
           <t>Downstream</t>
         </is>
       </c>
-      <c r="J4" s="38" t="inlineStr">
+      <c r="J4" s="28" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -3567,664 +3513,666 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:F32"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="46" customWidth="1" style="25" min="2" max="2"/>
-    <col width="15" customWidth="1" style="25" min="3" max="5"/>
-    <col width="32" customWidth="1" style="25" min="6" max="6"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Transaction, Operating, and Financing Assumptions</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Assumption</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Downside</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Active</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Units / note</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>LTM revenue</t>
         </is>
       </c>
-      <c r="C5" s="40" t="n">
+      <c r="C5" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="D5" s="40" t="n">
+      <c r="D5" s="9" t="n">
         <v>600</v>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="10">
         <f>IF(Cover!$C$9="Downside",D5,C5)</f>
         <v/>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>LTM EBITDA margin</t>
         </is>
       </c>
-      <c r="C6" s="42" t="n">
+      <c r="C6" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="42" t="n">
+      <c r="D6" s="11" t="n">
         <v>0.17</v>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="12">
         <f>IF(Cover!$C$9="Downside",D6,C6)</f>
         <v/>
       </c>
-      <c r="F6" s="25" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Annual revenue growth</t>
         </is>
       </c>
-      <c r="C7" s="42" t="n">
+      <c r="C7" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="D7" s="42" t="n">
+      <c r="D7" s="11" t="n">
         <v>-0.02</v>
       </c>
-      <c r="E7" s="43">
+      <c r="E7" s="12">
         <f>IF(Cover!$C$9="Downside",D7,C7)</f>
         <v/>
       </c>
-      <c r="F7" s="25" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Annual EBITDA margin expansion</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="13" t="n">
         <v>0.005</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="13" t="n">
         <v>-0.003</v>
       </c>
-      <c r="E8" s="45">
+      <c r="E8" s="14">
         <f>IF(Cover!$C$9="Downside",D8,C8)</f>
         <v/>
       </c>
-      <c r="F8" s="25" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>% points</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>D&amp;A / revenue</t>
         </is>
       </c>
-      <c r="C9" s="42" t="n">
+      <c r="C9" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="D9" s="42" t="n">
+      <c r="D9" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E9" s="43">
+      <c r="E9" s="12">
         <f>IF(Cover!$C$9="Downside",D9,C9)</f>
         <v/>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Capex / revenue</t>
         </is>
       </c>
-      <c r="C10" s="42" t="n">
+      <c r="C10" s="11" t="n">
         <v>0.035</v>
       </c>
-      <c r="D10" s="42" t="n">
+      <c r="D10" s="11" t="n">
         <v>0.045</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="12">
         <f>IF(Cover!$C$9="Downside",D10,C10)</f>
         <v/>
       </c>
-      <c r="F10" s="25" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>NWC / revenue</t>
         </is>
       </c>
-      <c r="C11" s="42" t="n">
+      <c r="C11" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="D11" s="42" t="n">
+      <c r="D11" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E11" s="43">
+      <c r="E11" s="12">
         <f>IF(Cover!$C$9="Downside",D11,C11)</f>
         <v/>
       </c>
-      <c r="F11" s="25" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cash tax rate</t>
         </is>
       </c>
-      <c r="C12" s="42" t="n">
+      <c r="C12" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="D12" s="42" t="n">
+      <c r="D12" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="E12" s="43">
+      <c r="E12" s="12">
         <f>IF(Cover!$C$9="Downside",D12,C12)</f>
         <v/>
       </c>
-      <c r="F12" s="25" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="25" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Entry EBITDA multiple</t>
         </is>
       </c>
-      <c r="C13" s="46" t="n">
+      <c r="C13" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D13" s="46" t="n">
+      <c r="D13" s="15" t="n">
         <v>9</v>
       </c>
-      <c r="E13" s="47">
+      <c r="E13" s="16">
         <f>IF(Cover!$C$9="Downside",D13,C13)</f>
         <v/>
       </c>
-      <c r="F13" s="25" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="25" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Transaction fees / enterprise value</t>
         </is>
       </c>
-      <c r="C14" s="42" t="n">
+      <c r="C14" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D14" s="42" t="n">
+      <c r="D14" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E14" s="43">
+      <c r="E14" s="12">
         <f>IF(Cover!$C$9="Downside",D14,C14)</f>
         <v/>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="25" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Existing net debt refinanced</t>
         </is>
       </c>
-      <c r="C15" s="40" t="n">
+      <c r="C15" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="D15" s="40" t="n">
+      <c r="D15" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="10">
         <f>IF(Cover!$C$9="Downside",D15,C15)</f>
         <v/>
       </c>
-      <c r="F15" s="25" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="B16" s="25" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Minimum cash</t>
         </is>
       </c>
-      <c r="C16" s="40" t="n">
+      <c r="C16" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="D16" s="40" t="n">
+      <c r="D16" s="9" t="n">
         <v>25</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="10">
         <f>IF(Cover!$C$9="Downside",D16,C16)</f>
         <v/>
       </c>
-      <c r="F16" s="25" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="B17" s="25" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Revolver commitment</t>
         </is>
       </c>
-      <c r="C17" s="40" t="n">
+      <c r="C17" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="D17" s="40" t="n">
+      <c r="D17" s="9" t="n">
         <v>75</v>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="10">
         <f>IF(Cover!$C$9="Downside",D17,C17)</f>
         <v/>
       </c>
-      <c r="F17" s="25" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>$mm</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="26">
-      <c r="B18" s="25" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Revolver cash rate</t>
         </is>
       </c>
-      <c r="C18" s="44" t="n">
+      <c r="C18" s="13" t="n">
         <v>0.09</v>
       </c>
-      <c r="D18" s="44" t="n">
+      <c r="D18" s="13" t="n">
         <v>0.115</v>
       </c>
-      <c r="E18" s="45">
+      <c r="E18" s="14">
         <f>IF(Cover!$C$9="Downside",D18,C18)</f>
         <v/>
       </c>
-      <c r="F18" s="25" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="26">
-      <c r="B19" s="25" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>TLB opening leverage</t>
         </is>
       </c>
-      <c r="C19" s="46" t="n">
+      <c r="C19" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="46" t="n">
+      <c r="D19" s="15" t="n">
         <v>3.5</v>
       </c>
-      <c r="E19" s="47">
+      <c r="E19" s="16">
         <f>IF(Cover!$C$9="Downside",D19,C19)</f>
         <v/>
       </c>
-      <c r="F19" s="25" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>x EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="26">
-      <c r="B20" s="25" t="inlineStr">
+    <row r="20">
+      <c r="B20" t="inlineStr">
         <is>
           <t>TLB cash rate</t>
         </is>
       </c>
-      <c r="C20" s="44" t="n">
+      <c r="C20" s="13" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D20" s="44" t="n">
+      <c r="D20" s="13" t="n">
         <v>0.105</v>
       </c>
-      <c r="E20" s="45">
+      <c r="E20" s="14">
         <f>IF(Cover!$C$9="Downside",D20,C20)</f>
         <v/>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="26">
-      <c r="B21" s="25" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>TLB annual amortization</t>
         </is>
       </c>
-      <c r="C21" s="42" t="n">
+      <c r="C21" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="D21" s="42" t="n">
+      <c r="D21" s="11" t="n">
         <v>0.01</v>
       </c>
-      <c r="E21" s="43">
+      <c r="E21" s="12">
         <f>IF(Cover!$C$9="Downside",D21,C21)</f>
         <v/>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>% original</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="26">
-      <c r="B22" s="25" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Second-lien opening leverage</t>
         </is>
       </c>
-      <c r="C22" s="46" t="n">
+      <c r="C22" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="D22" s="46" t="n">
+      <c r="D22" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="16">
         <f>IF(Cover!$C$9="Downside",D22,C22)</f>
         <v/>
       </c>
-      <c r="F22" s="25" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>x EBITDA</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="26">
-      <c r="B23" s="25" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Second-lien cash rate</t>
         </is>
       </c>
-      <c r="C23" s="44" t="n">
+      <c r="C23" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="D23" s="44" t="n">
+      <c r="D23" s="13" t="n">
         <v>0.13</v>
       </c>
-      <c r="E23" s="45">
+      <c r="E23" s="14">
         <f>IF(Cover!$C$9="Downside",D23,C23)</f>
         <v/>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="26">
-      <c r="B24" s="25" t="inlineStr">
+    <row r="24">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Second-lien PIK rate</t>
         </is>
       </c>
-      <c r="C24" s="44" t="n">
+      <c r="C24" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="D24" s="44" t="n">
+      <c r="D24" s="13" t="n">
         <v>0.05</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E24" s="14">
         <f>IF(Cover!$C$9="Downside",D24,C24)</f>
         <v/>
       </c>
-      <c r="F24" s="25" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="26">
-      <c r="B25" s="25" t="inlineStr">
+    <row r="25">
+      <c r="B25" t="inlineStr">
         <is>
           <t>Cash sweep</t>
         </is>
       </c>
-      <c r="C25" s="42" t="n">
+      <c r="C25" s="11" t="n">
         <v>0.75</v>
       </c>
-      <c r="D25" s="42" t="n">
+      <c r="D25" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="E25" s="43">
+      <c r="E25" s="12">
         <f>IF(Cover!$C$9="Downside",D25,C25)</f>
         <v/>
       </c>
-      <c r="F25" s="25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>% excess cash</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="26">
-      <c r="B26" s="25" t="inlineStr">
+    <row r="26">
+      <c r="B26" t="inlineStr">
         <is>
           <t>Maximum leverage covenant</t>
         </is>
       </c>
-      <c r="C26" s="46" t="n">
+      <c r="C26" s="15" t="n">
         <v>7</v>
       </c>
-      <c r="D26" s="46" t="n">
+      <c r="D26" s="15" t="n">
         <v>6.5</v>
       </c>
-      <c r="E26" s="47">
+      <c r="E26" s="16">
         <f>IF(Cover!$C$9="Downside",D26,C26)</f>
         <v/>
       </c>
-      <c r="F26" s="25" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="26">
-      <c r="B27" s="25" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Minimum interest coverage</t>
         </is>
       </c>
-      <c r="C27" s="46" t="n">
+      <c r="C27" s="15" t="n">
         <v>1.75</v>
       </c>
-      <c r="D27" s="46" t="n">
+      <c r="D27" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="E27" s="47">
+      <c r="E27" s="16">
         <f>IF(Cover!$C$9="Downside",D27,C27)</f>
         <v/>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="26">
-      <c r="B28" s="25" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Exit EBITDA multiple</t>
         </is>
       </c>
-      <c r="C28" s="46" t="n">
+      <c r="C28" s="15" t="n">
         <v>10</v>
       </c>
-      <c r="D28" s="46" t="n">
+      <c r="D28" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="E28" s="47">
+      <c r="E28" s="16">
         <f>IF(Cover!$C$9="Downside",D28,C28)</f>
         <v/>
       </c>
-      <c r="F28" s="25" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="26">
-      <c r="B29" s="25" t="inlineStr">
+    <row r="29">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Exit year</t>
         </is>
       </c>
-      <c r="C29" s="48" t="n">
+      <c r="C29" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="48" t="n">
+      <c r="D29" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="E29" s="49">
+      <c r="E29" s="18">
         <f>IF(Cover!$C$9="Downside",D29,C29)</f>
         <v/>
       </c>
-      <c r="F29" s="25" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="26">
-      <c r="B30" s="25" t="inlineStr">
+    <row r="30">
+      <c r="B30" t="inlineStr">
         <is>
           <t>Management equity pool</t>
         </is>
       </c>
-      <c r="C30" s="42" t="n">
+      <c r="C30" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="D30" s="42" t="n">
+      <c r="D30" s="11" t="n">
         <v>0.1</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="12">
         <f>IF(Cover!$C$9="Downside",D30,C30)</f>
         <v/>
       </c>
-      <c r="F30" s="25" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>% fully diluted</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="26">
-      <c r="B31" s="25" t="inlineStr">
+    <row r="31">
+      <c r="B31" t="inlineStr">
         <is>
           <t>Sponsor preferred return</t>
         </is>
       </c>
-      <c r="C31" s="42" t="n">
+      <c r="C31" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="D31" s="42" t="n">
+      <c r="D31" s="11" t="n">
         <v>0.08</v>
       </c>
-      <c r="E31" s="43">
+      <c r="E31" s="12">
         <f>IF(Cover!$C$9="Downside",D31,C31)</f>
         <v/>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="26">
-      <c r="B32" s="25" t="inlineStr">
+    <row r="32">
+      <c r="B32" t="inlineStr">
         <is>
           <t>Management catch-up above hurdle</t>
         </is>
       </c>
-      <c r="C32" s="42" t="n">
+      <c r="C32" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="D32" s="42" t="n">
+      <c r="D32" s="11" t="n">
         <v>0.2</v>
       </c>
-      <c r="E32" s="43">
+      <c r="E32" s="12">
         <f>IF(Cover!$C$9="Downside",D32,C32)</f>
         <v/>
       </c>
-      <c r="F32" s="25" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>% incremental</t>
         </is>
@@ -4234,167 +4182,165 @@
   <mergeCells count="1">
     <mergeCell ref="B2:F2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:G10"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="34" customWidth="1" style="25" min="2" max="2"/>
-    <col width="18" customWidth="1" style="25" min="3" max="3"/>
-    <col width="5" customWidth="1" style="25" min="4" max="4"/>
-    <col width="34" customWidth="1" style="25" min="5" max="5"/>
-    <col width="18" customWidth="1" style="25" min="6" max="6"/>
-    <col width="5" customWidth="1" style="25" min="7" max="7"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Transaction Sources &amp; Uses</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Uses</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="D4" s="39" t="n"/>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Sources</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="G4" s="39" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Purchase enterprise value</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="10">
         <f>Assumptions!E5*Assumptions!E6*Assumptions!E13</f>
         <v/>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Revolver at close</t>
         </is>
       </c>
-      <c r="F5" s="40" t="n">
+      <c r="F5" s="9" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Refinance existing net debt</t>
         </is>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="10">
         <f>Assumptions!E15</f>
         <v/>
       </c>
-      <c r="E6" s="25" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Term loan B</t>
         </is>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="10">
         <f>Assumptions!E5*Assumptions!E6*Assumptions!E19</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Transaction fees</t>
         </is>
       </c>
-      <c r="C7" s="41">
+      <c r="C7" s="10">
         <f>C5*Assumptions!E14</f>
         <v/>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Second-lien / holdco debt</t>
         </is>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="10">
         <f>Assumptions!E5*Assumptions!E6*Assumptions!E22</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Minimum cash funded</t>
         </is>
       </c>
-      <c r="C8" s="41">
+      <c r="C8" s="10">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="E8" s="25" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Sponsor equity</t>
         </is>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="10">
         <f>C9-SUM(F5:F7)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="50" t="inlineStr">
+    <row r="9">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Total uses</t>
         </is>
       </c>
-      <c r="C9" s="51">
+      <c r="C9" s="20">
         <f>SUM(C5:C8)</f>
         <v/>
       </c>
-      <c r="E9" s="50" t="inlineStr">
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>Total sources</t>
         </is>
       </c>
-      <c r="F9" s="51">
+      <c r="F9" s="20">
         <f>SUM(F5:F8)</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="E10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Sources less uses</t>
         </is>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="10">
         <f>F9-C9</f>
         <v/>
       </c>
@@ -4403,627 +4349,632 @@
   <mergeCells count="1">
     <mergeCell ref="B2:G2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:J19"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="36" customWidth="1" style="25" min="2" max="2"/>
-    <col width="13" customWidth="1" style="25" min="3" max="10"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Seven-Year Operating, Tax, and Cash Flow Model</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm / %</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>LTM</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="10">
         <f>Assumptions!E5</f>
         <v/>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="10">
         <f>C5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="10">
         <f>D5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="10">
         <f>E5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="10">
         <f>F5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="10">
         <f>G5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="10">
         <f>H5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="10">
         <f>I5*(1+Assumptions!$E$7)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="D6" s="43">
+      <c r="D6" s="12">
         <f>IFERROR(D5/C5-1,0)</f>
         <v/>
       </c>
-      <c r="E6" s="43">
+      <c r="E6" s="12">
         <f>IFERROR(E5/D5-1,0)</f>
         <v/>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="12">
         <f>IFERROR(F5/E5-1,0)</f>
         <v/>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="12">
         <f>IFERROR(G5/F5-1,0)</f>
         <v/>
       </c>
-      <c r="H6" s="43">
+      <c r="H6" s="12">
         <f>IFERROR(H5/G5-1,0)</f>
         <v/>
       </c>
-      <c r="I6" s="43">
+      <c r="I6" s="12">
         <f>IFERROR(I5/H5-1,0)</f>
         <v/>
       </c>
-      <c r="J6" s="43">
+      <c r="J6" s="12">
         <f>IFERROR(J5/I5-1,0)</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>EBITDA margin</t>
         </is>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="12">
         <f>Assumptions!E6</f>
         <v/>
       </c>
-      <c r="D7" s="43">
-        <f>MAX(0,MIN(0.6,C7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="E7" s="43">
-        <f>MAX(0,MIN(0.6,D7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="F7" s="43">
-        <f>MAX(0,MIN(0.6,E7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="G7" s="43">
-        <f>MAX(0,MIN(0.6,F7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="H7" s="43">
-        <f>MAX(0,MIN(0.6,G7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="I7" s="43">
-        <f>MAX(0,MIN(0.6,H7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-      <c r="J7" s="43">
-        <f>MAX(0,MIN(0.6,I7+Assumptions!$E$8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="50" t="inlineStr">
+      <c r="D7" s="12">
+        <f>MAX(0,MIN(0.60,C7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="E7" s="12">
+        <f>MAX(0,MIN(0.60,D7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="F7" s="12">
+        <f>MAX(0,MIN(0.60,E7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="G7" s="12">
+        <f>MAX(0,MIN(0.60,F7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="H7" s="12">
+        <f>MAX(0,MIN(0.60,G7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="I7" s="12">
+        <f>MAX(0,MIN(0.60,H7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+      <c r="J7" s="12">
+        <f>MAX(0,MIN(0.60,I7+Assumptions!$E$8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C8" s="51">
+      <c r="C8" s="20">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="51">
+      <c r="D8" s="20">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="51">
+      <c r="E8" s="20">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="20">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="20">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="51">
+      <c r="H8" s="20">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="51">
+      <c r="I8" s="20">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="51">
+      <c r="J8" s="20">
         <f>J5*J7</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="C9" s="41">
+      <c r="C9" s="10">
         <f>C5*Assumptions!E9</f>
         <v/>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="10">
         <f>D5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="10">
         <f>E5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="10">
         <f>F5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="10">
         <f>G5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="10">
         <f>H5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="10">
         <f>I5*Assumptions!$E$9</f>
         <v/>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="10">
         <f>J5*Assumptions!$E$9</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C10" s="41">
+      <c r="C10" s="10">
         <f>C8-C9</f>
         <v/>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="10">
         <f>D8-D9</f>
         <v/>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="10">
         <f>E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="10">
         <f>F8-F9</f>
         <v/>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="10">
         <f>G8-G9</f>
         <v/>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="10">
         <f>H8-H9</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="10">
         <f>I8-I9</f>
         <v/>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="10">
         <f>J8-J9</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="10">
         <f>'Debt Schedule'!D7</f>
         <v/>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="10">
         <f>'Debt Schedule'!E7</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="10">
         <f>'Debt Schedule'!F7</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="10">
         <f>'Debt Schedule'!G7</f>
         <v/>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="10">
         <f>'Debt Schedule'!H7</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="10">
         <f>'Debt Schedule'!I7</f>
         <v/>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="10">
         <f>'Debt Schedule'!J7</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>EBT</t>
         </is>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="10">
         <f>D10-D11</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="10">
         <f>E10-E11</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="10">
         <f>F10-F11</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="10">
         <f>G10-G11</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="10">
         <f>H10-H11</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="10">
         <f>I10-I11</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="10">
         <f>J10-J11</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="25" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Cash taxes</t>
         </is>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="10">
         <f>MAX(0,D12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="E13" s="41">
+      <c r="E13" s="10">
         <f>MAX(0,E12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="F13" s="41">
+      <c r="F13" s="10">
         <f>MAX(0,F12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="G13" s="41">
+      <c r="G13" s="10">
         <f>MAX(0,G12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="H13" s="41">
+      <c r="H13" s="10">
         <f>MAX(0,H12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="10">
         <f>MAX(0,I12*Assumptions!$E$12)</f>
         <v/>
       </c>
-      <c r="J13" s="41">
+      <c r="J13" s="10">
         <f>MAX(0,J12*Assumptions!$E$12)</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="25" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Net income</t>
         </is>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="10">
         <f>D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="10">
         <f>E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="10">
         <f>F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="10">
         <f>G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="10">
         <f>H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="10">
         <f>I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="10">
         <f>J12-J13</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="25" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Capex</t>
         </is>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="10">
         <f>D5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="10">
         <f>E5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="10">
         <f>F5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="10">
         <f>G5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="10">
         <f>H5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="10">
         <f>I5*Assumptions!$E$10</f>
         <v/>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="10">
         <f>J5*Assumptions!$E$10</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="B16" s="25" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>NWC</t>
         </is>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="10">
         <f>C5*Assumptions!E11</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="10">
         <f>D5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="10">
         <f>E5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="10">
         <f>F5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="10">
         <f>G5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="10">
         <f>H5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="10">
         <f>I5*Assumptions!$E$11</f>
         <v/>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="10">
         <f>J5*Assumptions!$E$11</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="B17" s="25" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Change in NWC</t>
         </is>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="10">
         <f>D16-C16</f>
         <v/>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="10">
         <f>E16-D16</f>
         <v/>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="10">
         <f>F16-E16</f>
         <v/>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="10">
         <f>G16-F16</f>
         <v/>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="10">
         <f>H16-G16</f>
         <v/>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="10">
         <f>I16-H16</f>
         <v/>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="10">
         <f>J16-I16</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="26">
-      <c r="B18" s="50" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>FCF before financing</t>
         </is>
       </c>
-      <c r="C18" s="51" t="n"/>
-      <c r="D18" s="51">
+      <c r="C18" s="20" t="n"/>
+      <c r="D18" s="20">
         <f>D14+D9-D15-D17</f>
         <v/>
       </c>
-      <c r="E18" s="51">
+      <c r="E18" s="20">
         <f>E14+E9-E15-E17</f>
         <v/>
       </c>
-      <c r="F18" s="51">
+      <c r="F18" s="20">
         <f>F14+F9-F15-F17</f>
         <v/>
       </c>
-      <c r="G18" s="51">
+      <c r="G18" s="20">
         <f>G14+G9-G15-G17</f>
         <v/>
       </c>
-      <c r="H18" s="51">
+      <c r="H18" s="20">
         <f>H14+H9-H15-H17</f>
         <v/>
       </c>
-      <c r="I18" s="51">
+      <c r="I18" s="20">
         <f>I14+I9-I15-I17</f>
         <v/>
       </c>
-      <c r="J18" s="51">
+      <c r="J18" s="20">
         <f>J14+J9-J15-J17</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="26">
-      <c r="B19" s="50" t="inlineStr">
+    <row r="19">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>FCF before interest</t>
         </is>
       </c>
-      <c r="C19" s="51" t="n"/>
-      <c r="D19" s="51">
+      <c r="C19" s="20" t="n"/>
+      <c r="D19" s="20">
         <f>D8-D13-D15-D17</f>
         <v/>
       </c>
-      <c r="E19" s="51">
+      <c r="E19" s="20">
         <f>E8-E13-E15-E17</f>
         <v/>
       </c>
-      <c r="F19" s="51">
+      <c r="F19" s="20">
         <f>F8-F13-F15-F17</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="20">
         <f>G8-G13-G15-G17</f>
         <v/>
       </c>
-      <c r="H19" s="51">
+      <c r="H19" s="20">
         <f>H8-H13-H15-H17</f>
         <v/>
       </c>
-      <c r="I19" s="51">
+      <c r="I19" s="20">
         <f>I8-I13-I15-I17</f>
         <v/>
       </c>
-      <c r="J19" s="51">
+      <c r="J19" s="20">
         <f>J8-J13-J15-J17</f>
         <v/>
       </c>
@@ -5032,965 +4983,970 @@
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:J28"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="42" customWidth="1" style="25" min="2" max="2"/>
-    <col width="13" customWidth="1" style="25" min="3" max="10"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Multi-Tranche Debt and Cash Sweep</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>$mm / %</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Close</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="J4" s="39" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Beginning cash</t>
         </is>
       </c>
-      <c r="C5" s="41">
+      <c r="C5" s="10">
         <f>Assumptions!E16</f>
         <v/>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="10">
         <f>C13</f>
         <v/>
       </c>
-      <c r="E5" s="41">
+      <c r="E5" s="10">
         <f>D13</f>
         <v/>
       </c>
-      <c r="F5" s="41">
+      <c r="F5" s="10">
         <f>E13</f>
         <v/>
       </c>
-      <c r="G5" s="41">
+      <c r="G5" s="10">
         <f>F13</f>
         <v/>
       </c>
-      <c r="H5" s="41">
+      <c r="H5" s="10">
         <f>G13</f>
         <v/>
       </c>
-      <c r="I5" s="41">
+      <c r="I5" s="10">
         <f>H13</f>
         <v/>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="10">
         <f>I13</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>FCF before interest</t>
         </is>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="10">
         <f>'Operating Model'!D19</f>
         <v/>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="10">
         <f>'Operating Model'!E19</f>
         <v/>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="10">
         <f>'Operating Model'!F19</f>
         <v/>
       </c>
-      <c r="G6" s="41">
+      <c r="G6" s="10">
         <f>'Operating Model'!G19</f>
         <v/>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="10">
         <f>'Operating Model'!H19</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="10">
         <f>'Operating Model'!I19</f>
         <v/>
       </c>
-      <c r="J6" s="41">
+      <c r="J6" s="10">
         <f>'Operating Model'!J19</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Cash interest</t>
         </is>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="10">
         <f>SUM(D15,D18,D23)</f>
         <v/>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="10">
         <f>SUM(E15,E18,E23)</f>
         <v/>
       </c>
-      <c r="F7" s="41">
+      <c r="F7" s="10">
         <f>SUM(F15,F18,F23)</f>
         <v/>
       </c>
-      <c r="G7" s="41">
+      <c r="G7" s="10">
         <f>SUM(G15,G18,G23)</f>
         <v/>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="10">
         <f>SUM(H15,H18,H23)</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="10">
         <f>SUM(I15,I18,I23)</f>
         <v/>
       </c>
-      <c r="J7" s="41">
+      <c r="J7" s="10">
         <f>SUM(J15,J18,J23)</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Mandatory TLB amortization</t>
         </is>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="10">
         <f>D19</f>
         <v/>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="10">
         <f>E19</f>
         <v/>
       </c>
-      <c r="F8" s="41">
+      <c r="F8" s="10">
         <f>F19</f>
         <v/>
       </c>
-      <c r="G8" s="41">
+      <c r="G8" s="10">
         <f>G19</f>
         <v/>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="10">
         <f>H19</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="10">
         <f>I19</f>
         <v/>
       </c>
-      <c r="J8" s="41">
+      <c r="J8" s="10">
         <f>J19</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Cash before revolver / sweep</t>
         </is>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="10">
         <f>D5+D6-D7-D8</f>
         <v/>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="10">
         <f>E5+E6-E7-E8</f>
         <v/>
       </c>
-      <c r="F9" s="41">
+      <c r="F9" s="10">
         <f>F5+F6-F7-F8</f>
         <v/>
       </c>
-      <c r="G9" s="41">
+      <c r="G9" s="10">
         <f>G5+G6-G7-G8</f>
         <v/>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="10">
         <f>H5+H6-H7-H8</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="10">
         <f>I5+I6-I7-I8</f>
         <v/>
       </c>
-      <c r="J9" s="41">
+      <c r="J9" s="10">
         <f>J5+J6-J7-J8</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Revolver draw / (repayment)</t>
         </is>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="10">
         <f>IF(D9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-D14,Assumptions!$E$16-D9),-MIN(D14,MAX(0,D9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="E10" s="41">
+      <c r="E10" s="10">
         <f>IF(E9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-E14,Assumptions!$E$16-E9),-MIN(E14,MAX(0,E9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="F10" s="41">
+      <c r="F10" s="10">
         <f>IF(F9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-F14,Assumptions!$E$16-F9),-MIN(F14,MAX(0,F9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="G10" s="41">
+      <c r="G10" s="10">
         <f>IF(G9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-G14,Assumptions!$E$16-G9),-MIN(G14,MAX(0,G9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="10">
         <f>IF(H9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-H14,Assumptions!$E$16-H9),-MIN(H14,MAX(0,H9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="10">
         <f>IF(I9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-I14,Assumptions!$E$16-I9),-MIN(I14,MAX(0,I9-Assumptions!$E$16)))</f>
         <v/>
       </c>
-      <c r="J10" s="41">
+      <c r="J10" s="10">
         <f>IF(J9&lt;Assumptions!$E$16,MIN(Assumptions!$E$17-J14,Assumptions!$E$16-J9),-MIN(J14,MAX(0,J9-Assumptions!$E$16)))</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Cash sweep to TLB</t>
         </is>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="10">
         <f>MIN(MAX(0,D17-D19),MAX(0,D9+D10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="10">
         <f>MIN(MAX(0,E17-E19),MAX(0,E9+E10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="10">
         <f>MIN(MAX(0,F17-F19),MAX(0,F9+F10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="10">
         <f>MIN(MAX(0,G17-G19),MAX(0,G9+G10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="10">
         <f>MIN(MAX(0,H17-H19),MAX(0,H9+H10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="10">
         <f>MIN(MAX(0,I17-I19),MAX(0,I9+I10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="J11" s="41">
+      <c r="J11" s="10">
         <f>MIN(MAX(0,J17-J19),MAX(0,J9+J10-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cash sweep to second lien</t>
         </is>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="10">
         <f>MIN(MAX(0,D22+D24),MAX(0,D9+D10-D11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="10">
         <f>MIN(MAX(0,E22+E24),MAX(0,E9+E10-E11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="10">
         <f>MIN(MAX(0,F22+F24),MAX(0,F9+F10-F11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="10">
         <f>MIN(MAX(0,G22+G24),MAX(0,G9+G10-G11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="10">
         <f>MIN(MAX(0,H22+H24),MAX(0,H9+H10-H11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="10">
         <f>MIN(MAX(0,I22+I24),MAX(0,I9+I10-I11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
-      <c r="J12" s="41">
+      <c r="J12" s="10">
         <f>MIN(MAX(0,J22+J24),MAX(0,J9+J10-J11-Assumptions!$E$16)*Assumptions!$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="50" t="inlineStr">
+    <row r="13">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>Ending cash</t>
         </is>
       </c>
-      <c r="C13" s="51">
+      <c r="C13" s="20">
         <f>C5</f>
         <v/>
       </c>
-      <c r="D13" s="51">
+      <c r="D13" s="20">
         <f>D9+D10-D11-D12</f>
         <v/>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="20">
         <f>E9+E10-E11-E12</f>
         <v/>
       </c>
-      <c r="F13" s="51">
+      <c r="F13" s="20">
         <f>F9+F10-F11-F12</f>
         <v/>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="20">
         <f>G9+G10-G11-G12</f>
         <v/>
       </c>
-      <c r="H13" s="51">
+      <c r="H13" s="20">
         <f>H9+H10-H11-H12</f>
         <v/>
       </c>
-      <c r="I13" s="51">
+      <c r="I13" s="20">
         <f>I9+I10-I11-I12</f>
         <v/>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="20">
         <f>J9+J10-J11-J12</f>
         <v/>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="26">
-      <c r="B14" s="25" t="inlineStr">
+    <row r="14">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Beginning revolver</t>
         </is>
       </c>
-      <c r="C14" s="41">
+      <c r="C14" s="10">
         <f>'Sources &amp; Uses'!F5</f>
         <v/>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="10">
         <f>C16</f>
         <v/>
       </c>
-      <c r="E14" s="41">
+      <c r="E14" s="10">
         <f>D16</f>
         <v/>
       </c>
-      <c r="F14" s="41">
+      <c r="F14" s="10">
         <f>E16</f>
         <v/>
       </c>
-      <c r="G14" s="41">
+      <c r="G14" s="10">
         <f>F16</f>
         <v/>
       </c>
-      <c r="H14" s="41">
+      <c r="H14" s="10">
         <f>G16</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="10">
         <f>H16</f>
         <v/>
       </c>
-      <c r="J14" s="41">
+      <c r="J14" s="10">
         <f>I16</f>
         <v/>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="26">
-      <c r="B15" s="25" t="inlineStr">
+    <row r="15">
+      <c r="B15" t="inlineStr">
         <is>
           <t>Revolver interest</t>
         </is>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="10">
         <f>D14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="E15" s="41">
+      <c r="E15" s="10">
         <f>E14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="F15" s="41">
+      <c r="F15" s="10">
         <f>F14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="G15" s="41">
+      <c r="G15" s="10">
         <f>G14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="H15" s="41">
+      <c r="H15" s="10">
         <f>H14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="10">
         <f>I14*Assumptions!$E$18</f>
         <v/>
       </c>
-      <c r="J15" s="41">
+      <c r="J15" s="10">
         <f>J14*Assumptions!$E$18</f>
         <v/>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="26">
-      <c r="B16" s="25" t="inlineStr">
+    <row r="16">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Ending revolver</t>
         </is>
       </c>
-      <c r="C16" s="41">
+      <c r="C16" s="10">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="10">
         <f>MAX(0,D14+D10)</f>
         <v/>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="10">
         <f>MAX(0,E14+E10)</f>
         <v/>
       </c>
-      <c r="F16" s="41">
+      <c r="F16" s="10">
         <f>MAX(0,F14+F10)</f>
         <v/>
       </c>
-      <c r="G16" s="41">
+      <c r="G16" s="10">
         <f>MAX(0,G14+G10)</f>
         <v/>
       </c>
-      <c r="H16" s="41">
+      <c r="H16" s="10">
         <f>MAX(0,H14+H10)</f>
         <v/>
       </c>
-      <c r="I16" s="41">
+      <c r="I16" s="10">
         <f>MAX(0,I14+I10)</f>
         <v/>
       </c>
-      <c r="J16" s="41">
+      <c r="J16" s="10">
         <f>MAX(0,J14+J10)</f>
         <v/>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="26">
-      <c r="B17" s="25" t="inlineStr">
+    <row r="17">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Beginning TLB</t>
         </is>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="10">
         <f>'Sources &amp; Uses'!F6</f>
         <v/>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="10">
         <f>C21</f>
         <v/>
       </c>
-      <c r="E17" s="41">
+      <c r="E17" s="10">
         <f>D21</f>
         <v/>
       </c>
-      <c r="F17" s="41">
+      <c r="F17" s="10">
         <f>E21</f>
         <v/>
       </c>
-      <c r="G17" s="41">
+      <c r="G17" s="10">
         <f>F21</f>
         <v/>
       </c>
-      <c r="H17" s="41">
+      <c r="H17" s="10">
         <f>G21</f>
         <v/>
       </c>
-      <c r="I17" s="41">
+      <c r="I17" s="10">
         <f>H21</f>
         <v/>
       </c>
-      <c r="J17" s="41">
+      <c r="J17" s="10">
         <f>I21</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="26">
-      <c r="B18" s="25" t="inlineStr">
+    <row r="18">
+      <c r="B18" t="inlineStr">
         <is>
           <t>TLB interest</t>
         </is>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="10">
         <f>D17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="E18" s="41">
+      <c r="E18" s="10">
         <f>E17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="F18" s="41">
+      <c r="F18" s="10">
         <f>F17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="G18" s="41">
+      <c r="G18" s="10">
         <f>G17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="H18" s="41">
+      <c r="H18" s="10">
         <f>H17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="I18" s="41">
+      <c r="I18" s="10">
         <f>I17*Assumptions!$E$20</f>
         <v/>
       </c>
-      <c r="J18" s="41">
+      <c r="J18" s="10">
         <f>J17*Assumptions!$E$20</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="26">
-      <c r="B19" s="25" t="inlineStr">
+    <row r="19">
+      <c r="B19" t="inlineStr">
         <is>
           <t>TLB amortization</t>
         </is>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="10">
         <f>MIN(D17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="10">
         <f>MIN(E17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="F19" s="41">
+      <c r="F19" s="10">
         <f>MIN(F17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="G19" s="41">
+      <c r="G19" s="10">
         <f>MIN(G17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="H19" s="41">
+      <c r="H19" s="10">
         <f>MIN(H17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="I19" s="41">
+      <c r="I19" s="10">
         <f>MIN(I17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
-      <c r="J19" s="41">
+      <c r="J19" s="10">
         <f>MIN(J17,'Sources &amp; Uses'!$F$6*Assumptions!$E$21)</f>
         <v/>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="26">
-      <c r="B20" s="50" t="inlineStr">
+    <row r="20">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>TLB cash sweep</t>
         </is>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="20">
         <f>'Sources &amp; Uses'!F7</f>
         <v/>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="20">
         <f>D11</f>
         <v/>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="20">
         <f>E11</f>
         <v/>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="20">
         <f>F11</f>
         <v/>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="20">
         <f>G11</f>
         <v/>
       </c>
-      <c r="H20" s="51">
+      <c r="H20" s="20">
         <f>H11</f>
         <v/>
       </c>
-      <c r="I20" s="51">
+      <c r="I20" s="20">
         <f>I11</f>
         <v/>
       </c>
-      <c r="J20" s="51">
+      <c r="J20" s="20">
         <f>J11</f>
         <v/>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="26">
-      <c r="B21" s="25" t="inlineStr">
+    <row r="21">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Ending TLB</t>
         </is>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="10">
         <f>C17</f>
         <v/>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="10">
         <f>MAX(0,D17-D19-D20)</f>
         <v/>
       </c>
-      <c r="E21" s="41">
+      <c r="E21" s="10">
         <f>MAX(0,E17-E19-E20)</f>
         <v/>
       </c>
-      <c r="F21" s="41">
+      <c r="F21" s="10">
         <f>MAX(0,F17-F19-F20)</f>
         <v/>
       </c>
-      <c r="G21" s="41">
+      <c r="G21" s="10">
         <f>MAX(0,G17-G19-G20)</f>
         <v/>
       </c>
-      <c r="H21" s="41">
+      <c r="H21" s="10">
         <f>MAX(0,H17-H19-H20)</f>
         <v/>
       </c>
-      <c r="I21" s="41">
+      <c r="I21" s="10">
         <f>MAX(0,I17-I19-I20)</f>
         <v/>
       </c>
-      <c r="J21" s="41">
+      <c r="J21" s="10">
         <f>MAX(0,J17-J19-J20)</f>
         <v/>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="26">
-      <c r="B22" s="25" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Beginning second lien</t>
         </is>
       </c>
-      <c r="C22" s="41">
+      <c r="C22" s="10">
         <f>'Sources &amp; Uses'!F7</f>
         <v/>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="10">
         <f>C26</f>
         <v/>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="10">
         <f>D26</f>
         <v/>
       </c>
-      <c r="F22" s="41">
+      <c r="F22" s="10">
         <f>E26</f>
         <v/>
       </c>
-      <c r="G22" s="41">
+      <c r="G22" s="10">
         <f>F26</f>
         <v/>
       </c>
-      <c r="H22" s="41">
+      <c r="H22" s="10">
         <f>G26</f>
         <v/>
       </c>
-      <c r="I22" s="41">
+      <c r="I22" s="10">
         <f>H26</f>
         <v/>
       </c>
-      <c r="J22" s="41">
+      <c r="J22" s="10">
         <f>I26</f>
         <v/>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="26">
-      <c r="B23" s="25" t="inlineStr">
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Second-lien cash interest</t>
         </is>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="10">
         <f>D22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="10">
         <f>E22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="F23" s="41">
+      <c r="F23" s="10">
         <f>F22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="G23" s="41">
+      <c r="G23" s="10">
         <f>G22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="H23" s="41">
+      <c r="H23" s="10">
         <f>H22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="I23" s="41">
+      <c r="I23" s="10">
         <f>I22*Assumptions!$E$23</f>
         <v/>
       </c>
-      <c r="J23" s="41">
+      <c r="J23" s="10">
         <f>J22*Assumptions!$E$23</f>
         <v/>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="26">
-      <c r="B24" s="50" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Second-lien PIK</t>
         </is>
       </c>
-      <c r="C24" s="51" t="n"/>
-      <c r="D24" s="51">
+      <c r="C24" s="20" t="n"/>
+      <c r="D24" s="20">
         <f>D22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="20">
         <f>E22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="F24" s="51">
+      <c r="F24" s="20">
         <f>F22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="20">
         <f>G22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="H24" s="51">
+      <c r="H24" s="20">
         <f>H22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="I24" s="51">
+      <c r="I24" s="20">
         <f>I22*Assumptions!$E$24</f>
         <v/>
       </c>
-      <c r="J24" s="51">
+      <c r="J24" s="20">
         <f>J22*Assumptions!$E$24</f>
         <v/>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="26">
-      <c r="B25" s="50" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>Second-lien cash sweep</t>
         </is>
       </c>
-      <c r="C25" s="51">
+      <c r="C25" s="20">
         <f>SUM(C16,C20,C13)</f>
         <v/>
       </c>
-      <c r="D25" s="51">
+      <c r="D25" s="20">
         <f>D12</f>
         <v/>
       </c>
-      <c r="E25" s="51">
+      <c r="E25" s="20">
         <f>E12</f>
         <v/>
       </c>
-      <c r="F25" s="51">
+      <c r="F25" s="20">
         <f>F12</f>
         <v/>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="20">
         <f>G12</f>
         <v/>
       </c>
-      <c r="H25" s="51">
+      <c r="H25" s="20">
         <f>H12</f>
         <v/>
       </c>
-      <c r="I25" s="51">
+      <c r="I25" s="20">
         <f>I12</f>
         <v/>
       </c>
-      <c r="J25" s="51">
+      <c r="J25" s="20">
         <f>J12</f>
         <v/>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="26">
-      <c r="B26" s="50" t="inlineStr">
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Ending second lien</t>
         </is>
       </c>
-      <c r="C26" s="51">
+      <c r="C26" s="20">
         <f>C22</f>
         <v/>
       </c>
-      <c r="D26" s="51">
+      <c r="D26" s="20">
         <f>MAX(0,D22+D24-D25)</f>
         <v/>
       </c>
-      <c r="E26" s="51">
+      <c r="E26" s="20">
         <f>MAX(0,E22+E24-E25)</f>
         <v/>
       </c>
-      <c r="F26" s="51">
+      <c r="F26" s="20">
         <f>MAX(0,F22+F24-F25)</f>
         <v/>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="20">
         <f>MAX(0,G22+G24-G25)</f>
         <v/>
       </c>
-      <c r="H26" s="51">
+      <c r="H26" s="20">
         <f>MAX(0,H22+H24-H25)</f>
         <v/>
       </c>
-      <c r="I26" s="51">
+      <c r="I26" s="20">
         <f>MAX(0,I22+I24-I25)</f>
         <v/>
       </c>
-      <c r="J26" s="51">
+      <c r="J26" s="20">
         <f>MAX(0,J22+J24-J25)</f>
         <v/>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="26">
-      <c r="B27" s="25" t="inlineStr">
+    <row r="27">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="C27" s="41">
+      <c r="C27" s="10">
         <f>SUM(C16,C21,C26)</f>
         <v/>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="10">
         <f>SUM(D16,D21,D26)</f>
         <v/>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="10">
         <f>SUM(E16,E21,E26)</f>
         <v/>
       </c>
-      <c r="F27" s="41">
+      <c r="F27" s="10">
         <f>SUM(F16,F21,F26)</f>
         <v/>
       </c>
-      <c r="G27" s="41">
+      <c r="G27" s="10">
         <f>SUM(G16,G21,G26)</f>
         <v/>
       </c>
-      <c r="H27" s="41">
+      <c r="H27" s="10">
         <f>SUM(H16,H21,H26)</f>
         <v/>
       </c>
-      <c r="I27" s="41">
+      <c r="I27" s="10">
         <f>SUM(I16,I21,I26)</f>
         <v/>
       </c>
-      <c r="J27" s="41">
+      <c r="J27" s="10">
         <f>SUM(J16,J21,J26)</f>
         <v/>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="26">
-      <c r="B28" s="25" t="inlineStr">
+    <row r="28">
+      <c r="B28" t="inlineStr">
         <is>
           <t>Net debt</t>
         </is>
       </c>
-      <c r="C28" s="41">
+      <c r="C28" s="10">
         <f>C27-C13</f>
         <v/>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="10">
         <f>D27-D13</f>
         <v/>
       </c>
-      <c r="E28" s="41">
+      <c r="E28" s="10">
         <f>E27-E13</f>
         <v/>
       </c>
-      <c r="F28" s="41">
+      <c r="F28" s="10">
         <f>F27-F13</f>
         <v/>
       </c>
-      <c r="G28" s="41">
+      <c r="G28" s="10">
         <f>G27-G13</f>
         <v/>
       </c>
-      <c r="H28" s="41">
+      <c r="H28" s="10">
         <f>H27-H13</f>
         <v/>
       </c>
-      <c r="I28" s="41">
+      <c r="I28" s="10">
         <f>I27-I13</f>
         <v/>
       </c>
-      <c r="J28" s="41">
+      <c r="J28" s="10">
         <f>J27-J13</f>
         <v/>
       </c>
@@ -5999,386 +5955,390 @@
   <mergeCells count="1">
     <mergeCell ref="B2:I2"/>
   </mergeCells>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="B2:I13"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="4" customWidth="1" style="25" min="1" max="1"/>
-    <col width="34" customWidth="1" style="25" min="2" max="2"/>
-    <col width="13" customWidth="1" style="25" min="3" max="9"/>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="2" ht="27.75" customHeight="1" s="26">
-      <c r="B2" s="27" t="inlineStr">
+    <row r="2" ht="28" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Lender Covenant and Liquidity Dashboard</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="26">
-      <c r="B4" s="39" t="inlineStr">
+    <row r="4">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="C4" s="39" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Year 1</t>
         </is>
       </c>
-      <c r="D4" s="39" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
         <is>
           <t>Year 2</t>
         </is>
       </c>
-      <c r="E4" s="39" t="inlineStr">
+      <c r="E4" s="8" t="inlineStr">
         <is>
           <t>Year 3</t>
         </is>
       </c>
-      <c r="F4" s="39" t="inlineStr">
+      <c r="F4" s="8" t="inlineStr">
         <is>
           <t>Year 4</t>
         </is>
       </c>
-      <c r="G4" s="39" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Year 5</t>
         </is>
       </c>
-      <c r="H4" s="39" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Year 6</t>
         </is>
       </c>
-      <c r="I4" s="39" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>Year 7</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="26">
-      <c r="B5" s="25" t="inlineStr">
+    <row r="5">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Gross leverage</t>
         </is>
       </c>
-      <c r="C5" s="47">
+      <c r="C5" s="16">
         <f>IFERROR('Debt Schedule'!D25/'Operating Model'!D8,0)</f>
         <v/>
       </c>
-      <c r="D5" s="47">
+      <c r="D5" s="16">
         <f>IFERROR('Debt Schedule'!E25/'Operating Model'!E8,0)</f>
         <v/>
       </c>
-      <c r="E5" s="47">
+      <c r="E5" s="16">
         <f>IFERROR('Debt Schedule'!F25/'Operating Model'!F8,0)</f>
         <v/>
       </c>
-      <c r="F5" s="47">
+      <c r="F5" s="16">
         <f>IFERROR('Debt Schedule'!G25/'Operating Model'!G8,0)</f>
         <v/>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="16">
         <f>IFERROR('Debt Schedule'!H25/'Operating Model'!H8,0)</f>
         <v/>
       </c>
-      <c r="H5" s="47">
+      <c r="H5" s="16">
         <f>IFERROR('Debt Schedule'!I25/'Operating Model'!I8,0)</f>
         <v/>
       </c>
-      <c r="I5" s="47">
+      <c r="I5" s="16">
         <f>IFERROR('Debt Schedule'!J25/'Operating Model'!J8,0)</f>
         <v/>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="26">
-      <c r="B6" s="25" t="inlineStr">
+    <row r="6">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Maximum leverage</t>
         </is>
       </c>
-      <c r="C6" s="47">
+      <c r="C6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="D6" s="47">
+      <c r="D6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="E6" s="47">
+      <c r="E6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="F6" s="47">
+      <c r="F6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="G6" s="47">
+      <c r="G6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="H6" s="47">
+      <c r="H6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
-      <c r="I6" s="47">
+      <c r="I6" s="16">
         <f>Assumptions!$E$26</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="26">
-      <c r="B7" s="25" t="inlineStr">
+    <row r="7">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Leverage headroom</t>
         </is>
       </c>
-      <c r="C7" s="47">
+      <c r="C7" s="16">
         <f>C6-C5</f>
         <v/>
       </c>
-      <c r="D7" s="47">
+      <c r="D7" s="16">
         <f>D6-D5</f>
         <v/>
       </c>
-      <c r="E7" s="47">
+      <c r="E7" s="16">
         <f>E6-E5</f>
         <v/>
       </c>
-      <c r="F7" s="47">
+      <c r="F7" s="16">
         <f>F6-F5</f>
         <v/>
       </c>
-      <c r="G7" s="47">
+      <c r="G7" s="16">
         <f>G6-G5</f>
         <v/>
       </c>
-      <c r="H7" s="47">
+      <c r="H7" s="16">
         <f>H6-H5</f>
         <v/>
       </c>
-      <c r="I7" s="47">
+      <c r="I7" s="16">
         <f>I6-I5</f>
         <v/>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="26">
-      <c r="B8" s="25" t="inlineStr">
+    <row r="8">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Interest coverage</t>
         </is>
       </c>
-      <c r="C8" s="47">
+      <c r="C8" s="16">
         <f>IFERROR('Operating Model'!D8/'Debt Schedule'!D7,0)</f>
         <v/>
       </c>
-      <c r="D8" s="47">
+      <c r="D8" s="16">
         <f>IFERROR('Operating Model'!E8/'Debt Schedule'!E7,0)</f>
         <v/>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="16">
         <f>IFERROR('Operating Model'!F8/'Debt Schedule'!F7,0)</f>
         <v/>
       </c>
-      <c r="F8" s="47">
+      <c r="F8" s="16">
         <f>IFERROR('Operating Model'!G8/'Debt Schedule'!G7,0)</f>
         <v/>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="16">
         <f>IFERROR('Operating Model'!H8/'Debt Schedule'!H7,0)</f>
         <v/>
       </c>
-      <c r="H8" s="47">
+      <c r="H8" s="16">
         <f>IFERROR('Operating Model'!I8/'Debt Schedule'!I7,0)</f>
         <v/>
       </c>
-      <c r="I8" s="47">
+      <c r="I8" s="16">
         <f>IFERROR('Operating Model'!J8/'Debt Schedule'!J7,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="26">
-      <c r="B9" s="25" t="inlineStr">
+    <row r="9">
+      <c r="B9" t="inlineStr">
         <is>
           <t>Minimum coverage</t>
         </is>
       </c>
-      <c r="C9" s="47">
+      <c r="C9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="D9" s="47">
+      <c r="D9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="E9" s="47">
+      <c r="E9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="F9" s="47">
+      <c r="F9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="G9" s="47">
+      <c r="G9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="H9" s="47">
+      <c r="H9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
-      <c r="I9" s="47">
+      <c r="I9" s="16">
         <f>Assumptions!$E$27</f>
         <v/>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="26">
-      <c r="B10" s="25" t="inlineStr">
+    <row r="10">
+      <c r="B10" t="inlineStr">
         <is>
           <t>Coverage headroom</t>
         </is>
       </c>
-      <c r="C10" s="47">
+      <c r="C10" s="16">
         <f>C8-C9</f>
         <v/>
       </c>
-      <c r="D10" s="47">
+      <c r="D10" s="16">
         <f>D8-D9</f>
         <v/>
       </c>
-      <c r="E10" s="47">
+      <c r="E10" s="16">
         <f>E8-E9</f>
         <v/>
       </c>
-      <c r="F10" s="47">
+      <c r="F10" s="16">
         <f>F8-F9</f>
         <v/>
       </c>
-      <c r="G10" s="47">
+      <c r="G10" s="16">
         <f>G8-G9</f>
         <v/>
       </c>
-      <c r="H10" s="47">
+      <c r="H10" s="16">
         <f>H8-H9</f>
         <v/>
       </c>
-      <c r="I10" s="47">
+      <c r="I10" s="16">
         <f>I8-I9</f>
         <v/>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="26">
-      <c r="B11" s="25" t="inlineStr">
+    <row r="11">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Minimum cash</t>
         </is>
       </c>
-      <c r="C11" s="41">
+      <c r="C11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="F11" s="41">
+      <c r="F11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="G11" s="41">
+      <c r="G11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="10">
         <f>Assumptions!$E$16</f>
         <v/>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="26">
-      <c r="B12" s="25" t="inlineStr">
+    <row r="12">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Cash headroom</t>
         </is>
       </c>
-      <c r="C12" s="41">
+      <c r="C12" s="10">
         <f>'Debt Schedule'!D13-C11</f>
         <v/>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="10">
         <f>'Debt Schedule'!E13-D11</f>
         <v/>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="10">
         <f>'Debt Schedule'!F13-E11</f>
         <v/>
       </c>
-      <c r="F12" s="41">
+      <c r="F12" s="10">
         <f>'Debt Schedule'!G13-F11</f>
         <v/>
       </c>
-      <c r="G12" s="41">
+      <c r="G12" s="10">
         <f>'Debt Schedule'!H13-G11</f>
         <v/>
       </c>
-      <c r="H12" s="41">
+      <c r="H12" s="10">
         <f>'Debt Schedule'!I13-H11</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="10">
         <f>'Debt Schedule'!J13-I11</f>
         <v/>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="26">
-      <c r="B13" s="25" t="inlineStr">
+    <row r="13">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13">
         <f>IF(AND(C7&gt;=0,C10&gt;=0,C12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13">
         <f>IF(AND(D7&gt;=0,D10&gt;=0,D12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13">
         <f>IF(AND(E7&gt;=0,E10&gt;=0,E12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13">
         <f>IF(AND(F7&gt;=0,F10&gt;=0,F12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13">
         <f>IF(AND(G7&gt;=0,G10&gt;=0,G12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13">
         <f>IF(AND(H7&gt;=0,H10&gt;=0,H12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13">
         <f>IF(AND(I7&gt;=0,I10&gt;=0,I12&gt;=0),"PASS","BREACH")</f>
         <v/>
       </c>
@@ -6388,21 +6348,19 @@
     <mergeCell ref="B2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="C13:I13">
-    <cfRule type="expression" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="1" dxfId="0">
       <formula>C13="PASS"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="3" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="2" dxfId="1">
       <formula>C13="FAIL"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="4" equalAverage="0" aboveAverage="0" dxfId="2" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="3" dxfId="2">
       <formula>C13="REVIEW"</formula>
     </cfRule>
-    <cfRule type="expression" rank="0" priority="5" equalAverage="0" aboveAverage="0" dxfId="1" text="" percent="0" bottom="0">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>C13="BREACH"</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/04_Merchant_Banking/_template_LBO.xlsx
+++ b/04_Merchant_Banking/_template_LBO.xlsx
@@ -3517,7 +3517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F32"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4175,6 +4175,28 @@
       <c r="F32" t="inlineStr">
         <is>
           <t>% incremental</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Revolver commitment fee (undrawn balance)</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="n">
+        <v>0.00375</v>
+      </c>
+      <c r="D33" s="13" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="E33" s="14">
+        <f>IF(Cover!$C$9="Downside",D33,C33)</f>
+        <v/>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>% p.a.</t>
         </is>
       </c>
     </row>
@@ -4993,7 +5015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J28"/>
+  <dimension ref="B2:J29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5143,31 +5165,31 @@
         </is>
       </c>
       <c r="D7" s="10">
-        <f>SUM(D15,D18,D23)</f>
+        <f>SUM(D15,D18,D23,D29)</f>
         <v/>
       </c>
       <c r="E7" s="10">
-        <f>SUM(E15,E18,E23)</f>
+        <f>SUM(E15,E18,E23,E29)</f>
         <v/>
       </c>
       <c r="F7" s="10">
-        <f>SUM(F15,F18,F23)</f>
+        <f>SUM(F15,F18,F23,F29)</f>
         <v/>
       </c>
       <c r="G7" s="10">
-        <f>SUM(G15,G18,G23)</f>
+        <f>SUM(G15,G18,G23,G29)</f>
         <v/>
       </c>
       <c r="H7" s="10">
-        <f>SUM(H15,H18,H23)</f>
+        <f>SUM(H15,H18,H23,H29)</f>
         <v/>
       </c>
       <c r="I7" s="10">
-        <f>SUM(I15,I18,I23)</f>
+        <f>SUM(I15,I18,I23,I29)</f>
         <v/>
       </c>
       <c r="J7" s="10">
-        <f>SUM(J15,J18,J23)</f>
+        <f>SUM(J15,J18,J23,J29)</f>
         <v/>
       </c>
     </row>
@@ -5948,6 +5970,41 @@
       </c>
       <c r="J28" s="10">
         <f>J27-J13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Revolver commitment fee (undrawn balance)</t>
+        </is>
+      </c>
+      <c r="D29" s="10">
+        <f>MAX(0,Assumptions!$E$17-D14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="E29" s="10">
+        <f>MAX(0,Assumptions!$E$17-E14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>MAX(0,Assumptions!$E$17-F14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="G29" s="10">
+        <f>MAX(0,Assumptions!$E$17-G14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="H29" s="10">
+        <f>MAX(0,Assumptions!$E$17-H14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="I29" s="10">
+        <f>MAX(0,Assumptions!$E$17-I14)*Assumptions!$E$33</f>
+        <v/>
+      </c>
+      <c r="J29" s="10">
+        <f>MAX(0,Assumptions!$E$17-J14)*Assumptions!$E$33</f>
         <v/>
       </c>
     </row>
